--- a/templates/Schulbegleiter-Import.xlsx
+++ b/templates/Schulbegleiter-Import.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="8">
   <si>
     <t>Vorname</t>
   </si>
@@ -23,6 +23,9 @@
     <t>Nachname</t>
   </si>
   <si>
+    <t>E-Mail</t>
+  </si>
+  <si>
     <t>Kommentar</t>
   </si>
   <si>
@@ -30,6 +33,9 @@
   </si>
   <si>
     <t>Beispiel</t>
+  </si>
+  <si>
+    <t>e.beispiel@schule.de</t>
   </si>
   <si>
     <t>Begleitet vormittags</t>
@@ -382,15 +388,16 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="10.569" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="24.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="24.708" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -400,16 +407,22 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
